--- a/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_21-10-2026.xlsx
+++ b/Compititor's_Price/Core-Products_Prices/Core-Products_Prices_21-10-2026.xlsx
@@ -499,36 +499,35 @@
       <c r="D2" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -582,36 +581,35 @@
       <c r="D3" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -642,7 +640,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t>£30.28</t>
         </is>
       </c>
     </row>
@@ -665,36 +663,35 @@
       <c r="D4" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -747,173 +744,171 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>£34.99</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>£31.34</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>£44.94</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>£31.99</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>£31.34</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>£30.52</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>KNAPR25N</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Knauf Acoustic Partition Roll 25mm 4 x 600mm (26.64m2)</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>£44.05</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>£34.99</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>£31.34</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>£44.94</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>£31.99</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>£31.34</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>£43.99</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>£42.79</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>£64.27</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>£45.6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>£42.79</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>KNAPR25N</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Knauf Acoustic Partition Roll 25mm 4 x 600mm (26.64m2)</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>£44.05</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>KNAPR50N</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Knauf Acoustic Partition Roll 50mm 2 x 600mm (16.2m2)</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>£44.07</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>£43.99</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>£42.79</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>£64.27</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>£45.6</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>£42.79</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>£44.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>KNAPR50N</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Knauf Acoustic Partition Roll 50mm 2 x 600mm (16.2m2)</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>£44.07</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -965,7 +960,37 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=156.0.8078.47)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
+</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -1018,36 +1043,35 @@
       <c r="D9" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -1152,92 +1176,91 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>£47.24</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>£35.8</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>£36.29</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>£35.81</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>£37.37</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>D-37-75mm</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Knauf DriTherm 37 75mm x 1.2m x 0.455m (4.37m2)</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>£20.45</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>£47.24</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>£35.8</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>£36.29</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>£35.81</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>£37.37</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>D-37-75mm</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Knauf DriTherm 37 75mm x 1.2m x 0.455m (4.37m2)</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>£20.45</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
       <c r="E12" t="inlineStr">
         <is>
           <t>£22.49</t>
@@ -1245,7 +1268,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>£31.34</t>
+          <t>£27.69</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1287,7 +1310,37 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=156.0.8078.47)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -1392,36 +1445,35 @@
       <c r="D15" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -1475,36 +1527,35 @@
       <c r="D16" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -1558,36 +1609,35 @@
       <c r="D17" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -1692,7 +1742,37 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Price Not Found</t>
+          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
+  (Session info: chrome=156.0.8078.47)
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1744,173 +1824,171 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>£46.78</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>£42.65</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>£49.9</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>£42.74</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>£42.66</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>£43.36</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>rwfl140.6</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Rockwool Flexi-Slab 140mm x 1200mm x 600mm (1 pack)</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>£38.99</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>£46.78</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>£42.65</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>£44.26</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>£39.27</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>£49.9</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>£42.74</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>£42.66</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>£43.36</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>rwfl140.6</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Rockwool Flexi-Slab 140mm x 1200mm x 600mm (1 pack)</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>£38.99</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>£39.9</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>£39.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>£42.01</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>rwfl100400</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Rockwool Flexi Slab 100mm x 1.2m x 0.4m (2.88m2)</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>£898.50</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>£44.26</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>£39.27</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>£49.9</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>£39.9</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>£39.0</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>£42.01</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>rwfl100400</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Rockwool Flexi Slab 100mm x 1.2m x 0.4m (2.88m2)</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>£898.50</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -2015,36 +2093,35 @@
       <c r="D24" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -2202,36 +2279,35 @@
       <c r="D27" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -2337,36 +2413,35 @@
       <c r="D29" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
@@ -2419,175 +2494,173 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>£174.96</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>£44.62</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>£186.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TF70 100mm</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Kingspan Thermafloor TF70 Floor Board 100mm (3 boards) 2.4m x 1.2m</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>£193.91</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>£174.96</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>£44.62</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>£157.14</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>£53.44</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
         <is>
           <t>Price Not Found</t>
         </is>
       </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>£186.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TF70 100mm</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Kingspan Thermafloor TF70 Floor Board 100mm (3 boards) 2.4m x 1.2m</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>£193.91</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>£173.05</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>TF70 120mm</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Kingspan TF70 120mm x 2.4m x 1.2m (2 Sh / 5.76m2)</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>£155.43</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>£157.14</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>£53.44</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>£173.05</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>TF70 120mm</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Kingspan TF70 120mm x 2.4m x 1.2m (2 Sh / 5.76m2)</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>£155.43</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Price Not Found</t>
-        </is>
-      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>N/L</t>
@@ -2605,7 +2678,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>£65.55</t>
+          <t>POA</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2637,504 +2710,468 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>Price Not Found</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>£179.08</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>£182.0</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>POA</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>£182.99</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>£182.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>£187.58</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>TR27 150mm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kingspan TR27 150mm x 1.2m x 1.2m (2 Sh / 2.88m2)</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>£139.95</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
-        <is>
-          <t>£179.08</t>
-        </is>
-      </c>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>£182.0</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>£131.78</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>£128.0</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>POA</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr">
-        <is>
-          <t>£182.99</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>£182.0</t>
-        </is>
-      </c>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>£187.58</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>TR27 150mm</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Kingspan TR27 150mm x 1.2m x 1.2m (2 Sh / 2.88m2)</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>£139.95</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>£128.99</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>£128.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>£132.69</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>K10690</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Kingspan K106 90mm</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>£96.45</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>£131.78</t>
-        </is>
-      </c>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>£128.0</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr">
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>£93.0</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>£87.5</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
         <is>
           <t>POA</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>£128.99</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>£128.0</t>
-        </is>
-      </c>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>£132.69</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>K10690</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Kingspan K106 90mm</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>£96.45</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>£89.58</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>£87.5</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>£88.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>Knte12.551200x2400</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Knauf Wallboard Tapered Edge 12.5mm x 1200mm x 2400mm </t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>£9.30</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
-        <is>
-          <t>£93.0</t>
-        </is>
-      </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>£87.5</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr">
-        <is>
-          <t>POA</t>
-        </is>
-      </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>£89.58</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>£87.5</t>
-        </is>
-      </c>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>£88.75</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Knte12.551200x2400</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Knauf Wallboard Tapered Edge 12.5mm x 1200mm x 2400mm </t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>£9.30</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>£9.23</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>£8.88</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>£7.36</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>£9.56</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>£8.92</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>£10.03</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>sqt75</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foil Tape 75mm x 45m </t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>£8.95</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>N/L</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>£11.25</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>£6.42</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>£5.2</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>£10.99</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>£6.42</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>£4.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>knbond/adh25</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Knauf Bonding Compound Plasterboard Adhesive 25Kg</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>£9.92</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="E38" t="inlineStr">
         <is>
           <t>£9.23</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>£8.88</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr">
-        <is>
-          <t>£7.36</t>
-        </is>
-      </c>
-      <c r="H36" t="inlineStr">
-        <is>
-          <t>£9.56</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>£8.92</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>£10.03</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>sqt75</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Foil Tape 75mm x 45m </t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>£8.95</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>N/L</t>
-        </is>
-      </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>£11.25</t>
-        </is>
-      </c>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>£6.42</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>£5.2</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>£10.99</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>£6.42</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>£4.64</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>knbond/adh25</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Knauf Bonding Compound Plasterboard Adhesive 25Kg</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>£9.92</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>£9.68</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>£13.05</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>£14.9</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>£10.64</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>£11.0</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gypmf</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>BG Thistle Multi-Finish 25Kg</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>£10.18</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
         <is>
           <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
+  (Session info: chrome=156.0.8078.47)
 Stacktrace:
 Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
-</t>
-        </is>
-      </c>
-      <c r="E38" t="inlineStr">
-        <is>
-          <t>£9.23</t>
-        </is>
-      </c>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>£9.68</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr">
-        <is>
-          <t>£13.05</t>
-        </is>
-      </c>
-      <c r="H38" t="inlineStr">
-        <is>
-          <t>£14.9</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>£10.64</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>£11.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>gypmf</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>BG Thistle Multi-Finish 25Kg</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>£10.18</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Error: Message: unknown error: net::ERR_PROXY_CONNECTION_FAILED
-  (Session info: chrome=155.0.8059.80)
-Stacktrace:
-Symbols not available. Dumping unresolved backtrace:
-	(No symbol) [0x7ff6ecdfe745]
-	(No symbol) [0x7ff6ec9b3d00]
-	(No symbol) [0x7ff6ec7e3f3d]
-	(No symbol) [0x7ff6ec7e0d05]
-	(No symbol) [0x7ff6ec7d15f1]
-	(No symbol) [0x7ff6ec7d343b]
-	(No symbol) [0x7ff6ec7d1b84]
-	(No symbol) [0x7ff6ec7d135b]
-	(No symbol) [0x7ff6ec7d1011]
-	(No symbol) [0x7ff6ec7cecfa]
-	(No symbol) [0x7ff6ec7cf452]
-	(No symbol) [0x7ff6ec7e8237]
-	(No symbol) [0x7ff6ec895914]
-	(No symbol) [0x7ff6ec868ada]
-	(No symbol) [0x7ff6ec894b5a]
-	(No symbol) [0x7ff6ec831462]
-	(No symbol) [0x7ff6ec832273]
-	(No symbol) [0x7ff6ecea17b1]
-	(No symbol) [0x7ff6eced87c7]
-	(No symbol) [0x7ff6ececc85e]
-	(No symbol) [0x7ff6ecb7884e]
-	(No symbol) [0x7ff6ec9c0415]
-	(No symbol) [0x7ff6ec9bbdf4]
-	(No symbol) [0x7ff6ec9bbf84]
-	(No symbol) [0x7ff6ec9a7f7c]
-	(No symbol) [0x7ffe816edda7]
-	(No symbol) [0x7ffe81e5ee4c]
+	(No symbol) [0x7ff795e03f45]
+	(No symbol) [0x7ff795d04f90]
+	(No symbol) [0x7ff795b82c53]
+	(No symbol) [0x7ff79639c121]
+	(No symbol) [0x7ff795b78ba7]
+	(No symbol) [0x7ff7961086af]
+	(No symbol) [0x7ff796107a86]
+	(No symbol) [0x7ff796107b4a]
+	(No symbol) [0x7ff795b7628d]
+	(No symbol) [0x7ff795b771b2]
+	(No symbol) [0x7ff795b83dc0]
+	(No symbol) [0x7ff795bb34f4]
+	(No symbol) [0x7ff795ba9a8a]
+	(No symbol) [0x7ff795bb25d1]
+	(No symbol) [0x7ff795b97cb9]
+	(No symbol) [0x7ff795b98ff3]
+	(No symbol) [0x7ff7962be1a1]
+	(No symbol) [0x7ff7962e181b]
+	(No symbol) [0x7ff7962d7ece]
+	(No symbol) [0x7ff795f2b10e]
+	(No symbol) [0x7ff795d13db5]
+	(No symbol) [0x7ff795d0e694]
+	(No symbol) [0x7ff795d0e824]
+	(No symbol) [0x7ff795cf6bdc]
+	(No symbol) [0x7fff790edda7]
+	(No symbol) [0x7fff79f5ee4c]
 </t>
         </is>
       </c>
